--- a/output/pdf_financials_xlsx/WGLD.xlsx
+++ b/output/pdf_financials_xlsx/WGLD.xlsx
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.161193</v>
+        <v>-0.161193</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.044519</v>
+        <v>-0.044519</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.161193</v>
+        <v>-0.161193</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.044519</v>
+        <v>-0.044519</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.161193</v>
+        <v>-0.161193</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.044519</v>
+        <v>-0.044519</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.445251</v>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.791033</v>
+        <v>-1.791033</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.161193</v>
+        <v>-0.161193</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.044519</v>
+        <v>-0.044519</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.161193</v>
+        <v>-0.161193</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.044519</v>
+        <v>-0.044519</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0.161193</v>
+        <v>-0.161193</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>0.044519</v>
+        <v>-0.044519</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WGLD.xlsx
+++ b/output/pdf_financials_xlsx/WGLD.xlsx
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.161193</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.044519</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.161193</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.044519</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.77284</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.741214</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.447733</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.781511</v>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.77284</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.741214</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.447733</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.781511</v>
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.77284</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.741214</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.747907</v>
+        <v>0.300174</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.037871</v>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">

--- a/output/pdf_financials_xlsx/WGLD.xlsx
+++ b/output/pdf_financials_xlsx/WGLD.xlsx
@@ -548,10 +548,8 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -618,10 +616,8 @@
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -650,10 +646,8 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -682,10 +676,8 @@
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>0.735076</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0.644413</v>
@@ -714,10 +706,8 @@
       <c r="C10" s="3" t="n">
         <v>0.044519</v>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D10" s="3" t="n">
+        <v>0.735076</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.644413</v>
@@ -784,10 +774,8 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -816,10 +804,8 @@
       <c r="C13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>-0</v>
@@ -848,10 +834,8 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
@@ -880,10 +864,8 @@
       <c r="C15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -912,10 +894,8 @@
       <c r="C16" s="3" t="n">
         <v>-0.044519</v>
       </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D16" s="3" t="n">
+        <v>-1.445251</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-2.563085</v>
@@ -944,10 +924,8 @@
       <c r="C17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1060,10 +1038,8 @@
       <c r="C20" s="3" t="n">
         <v>-0.044519</v>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D20" s="3" t="n">
+        <v>-1.445251</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-2.563085</v>
@@ -1092,10 +1068,8 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -1124,10 +1098,8 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
@@ -1300,10 +1272,8 @@
       <c r="C27" s="3" t="n">
         <v>-0.044519</v>
       </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D27" s="3" t="n">
+        <v>-1.445251</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.563085</v>
@@ -1332,10 +1302,8 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -1364,10 +1332,8 @@
       <c r="C29" s="3" t="n">
         <v>-0.044519</v>
       </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D29" s="3" t="n">
+        <v>-1.445251</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.563085</v>
@@ -1438,10 +1404,8 @@
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -4435,7 +4399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K175"/>
+  <dimension ref="A1:K214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9575,15 +9539,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="5" t="n">
+        <v>0.025126</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>0.007595</v>
       </c>
       <c r="I105" s="5" t="n">
         <v>0.025126</v>
@@ -11047,10 +11007,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="5" t="n">
+        <v>0.025126</v>
       </c>
       <c r="H135" s="5" t="n">
         <v>0.025126</v>
@@ -11996,10 +11954,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G154" s="5" t="n">
+        <v>4.658987</v>
       </c>
       <c r="H154" s="5" t="n">
         <v>4.658987</v>
@@ -12045,10 +12001,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G155" s="5" t="n">
+        <v>-2.086661</v>
       </c>
       <c r="H155" s="5" t="n">
         <v>-2.086661</v>
@@ -12645,10 +12599,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G167" s="5" t="n">
+        <v>0.002022</v>
       </c>
       <c r="H167" s="5" t="n">
         <v>0.002023</v>
@@ -12675,20 +12627,24 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Incorporation on</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>For the Year January</t>
+          <t>Balance, December 31 2020 $ - $</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -12724,24 +12680,24 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="n">
-        <v>0.010886</v>
-      </c>
-      <c r="F169" s="5" t="n">
-        <v>0.03244</v>
+          <t>Balance, December 31, 2021 -</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -12777,20 +12733,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated amortization</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Regulatory and filing fees</t>
+          <t>Balance, December 31 2020 $ - $</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" s="5" t="n">
-        <v>0.024307</v>
-      </c>
-      <c r="F170" s="5" t="n">
-        <v>0.012079</v>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -12826,17 +12786,23 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated amortization</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" s="5" t="n">
-        <v>0.126</v>
+          <t>Amortization -</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -12877,24 +12843,24 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated amortization</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E172" s="5" t="n">
-        <v>0.161193</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>0.044519</v>
+          <t>Balance, December 31, 2021 -</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -12930,34 +12896,34 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated amortization</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
+          <t>Amortization 1,315</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="n">
-        <v>-0.161193</v>
-      </c>
-      <c r="F173" s="5" t="n">
-        <v>-0.044519</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.002262</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>0.000947</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -12983,34 +12949,30 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated amortization</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (note 6) $</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="n">
-        <v>9e-08</v>
-      </c>
-      <c r="F174" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, December 31, 2022 $1,315</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.002262</v>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>0.000947</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -13036,46 +12998,2001 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
+          <t>Accumulated amortization</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Net book value – December 31, 2021 -</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Accumulated amortization</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Net book value – December 31, 2022 $16,216</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.022864</v>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>0.006648</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Properties            Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Balance – December 31, 2020 $ 553,050 $</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>1.1061</v>
+      </c>
+      <c r="H177" s="5" t="n">
+        <v>0.55305</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Properties            Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Balance – December 31, 2021 553,050 553</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>1.1061</v>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Properties            Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Impairment provision (553,050)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.55305</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Properties            Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Balance – December 30, 2022 -</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.55305</v>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>0.55305</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Cumulative Expenses - December 31, 2020 $ 836,937</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>2.026243</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>1.189306</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Consulting 122,637</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>0.341015</v>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>0.218378</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Drilling and fieldwork 525,382</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.903459</v>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>0.378077</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Lease rentals and other 28,298</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0.056597</v>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>0.028299</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Research and development tax credits (143,210)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>-0.275025</v>
+      </c>
+      <c r="H185" s="5" t="n">
+        <v>-0.131815</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Changes in 2021 533,107</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>1.026046</v>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>0.492939</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Cumulative Expenses - December 31, 2021 1,370,044</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>3.052289</v>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>1.682245</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Consulting 142,830</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>0.394061</v>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>0.251231</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Drilling and fieldwork 359,843</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.788752</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>0.428908</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Lease rentals and other 70,734</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>0.167121</v>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>0.096388</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Research and development tax credits 143,210</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>0.256764</v>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>0.113554</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Exploration and Evaluation Expenses             Knapdale     Lagalochan             Total</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Changes in 2022 716,617</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>1.606698</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>0.890081</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Cumulative Expenses before property</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Cumulative expenses – December 31, 2022 -</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>2.572326</v>
+      </c>
+      <c r="H193" s="5" t="n">
+        <v>2.572326</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Stock Options              Exercise Price</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Balance - December 31, 2020</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>4.4e-07</v>
+      </c>
+      <c r="H194" s="5" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Stock Options              Exercise Price</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Forfeited – October 2021</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>2.5e-07</v>
+      </c>
+      <c r="H195" s="5" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Stock Options              Exercise Price</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Balance - December 31, 2021</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>4.8e-07</v>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Stock Options              Exercise Price</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Changes in the period</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Stock Options              Exercise Price</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Balance – December 30, 2022</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>4.8e-07</v>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Options by Expiry Date                        Options   Exercise Price               Years</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>July 2, 2023 500,000</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>5e-07</v>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>5e-07</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Options by Expiry Date                        Options   Exercise Price               Years</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>December 8, 2025 1,275,000</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>2.9e-06</v>
+      </c>
+      <c r="H200" s="5" t="n">
+        <v>5e-07</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Options by Expiry Date                        Options   Exercise Price               Years</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>September 6, 2028 140,000</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>5.7e-06</v>
+      </c>
+      <c r="H201" s="5" t="n">
+        <v>2.5e-07</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Options by Expiry Date                        Options   Exercise Price               Years</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Total options and weighted averages 1,915,000</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>2.5e-06</v>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>4.8e-07</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>e)  Warrants</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>1,625,000 common shares at an exercise price of $0.75 per common share for a period of eighteen months. The warrants expired on June</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="H203" s="5" t="n">
+        <v>2.3e-05</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>e)  Warrants</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3,833,323 common shares at an exercise price of $0.25 per common share for a period of twelve months. The warrants expire on August</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="H204" s="5" t="n">
+        <v>2.5e-05</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Incorporation on</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>For the Year January</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n">
+        <v>0.010886</v>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>0.03244</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Regulatory and filing fees</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>0.024307</v>
+      </c>
+      <c r="F207" s="5" t="n">
+        <v>0.012079</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Share based compensation</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>0.161193</v>
+      </c>
+      <c r="F209" s="5" t="n">
+        <v>0.044519</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>-0.161193</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>-0.044519</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (note 6) $</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="n">
+        <v>9e-08</v>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
         <is>
           <t>Weighted average number of common shares</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E175" s="5" t="n">
+      <c r="E212" s="5" t="n">
         <v>1.844311</v>
       </c>
-      <c r="F175" s="5" t="n">
+      <c r="F212" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Share based compensation $</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" s="5" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="n">
+        <v>0.010886</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
